--- a/artfynd/A 12013-2023 artfynd.xlsx
+++ b/artfynd/A 12013-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12013-2023 artfynd.xlsx
+++ b/artfynd/A 12013-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1835,6 +1835,272 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114954419</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97545</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Fröseke, Svartegöl SO, Fröseke, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>548073</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6310139</v>
+      </c>
+      <c r="S12" t="n">
+        <v>61</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>G-Upp-0745</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>En polygon med fem angivna punkter enligt följande. 1.1499074-6311686: 39 skott. 2.1499072-6311768: 53 skott. 3.1499064-6311711: 7 skott. 4.1499081-6311789: 25 skott. 5. 1499103-6311791:16 skott. Summa: 140 skott.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114954520</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97545</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Fröseke, Svartegöl SO 2., Fröseke, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>548247</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6310088</v>
+      </c>
+      <c r="S13" t="n">
+        <v>46</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älghult</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>G-Upp-0746</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-05-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tre angivna punkter enligt följande: 1.1499220-6311714: 7 skott. 2.1499276-6311675: 38 skott. 3.1499200-6311639: 7 skott. Summa: 52 skott.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
